--- a/vSPD_Overrides/vSPD_Overrides.xlsx
+++ b/vSPD_Overrides/vSPD_Overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\vSPD\vSPD_Overrides\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB06F1B-6044-4430-BE20-EC40FACF4823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB51E2E-0E52-4948-A7E0-279DBAB2E8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -36772,10 +36772,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="1" max="1" width="28" style="26" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="15" style="26" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -36828,10 +36828,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="1" max="1" width="28" style="26" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="15" style="26" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -36884,10 +36884,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="1" max="1" width="28" style="26" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="15" style="26" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -36940,11 +36940,11 @@
   <dimension ref="A1:H96668"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="1" max="1" width="28" style="26" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
+    <col min="4" max="5" width="21.28515625" style="26" customWidth="1"/>
+    <col min="6" max="6" width="15" style="26" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
     <col min="8" max="8" width="36.140625" customWidth="1"/>
   </cols>
@@ -37265,10 +37265,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="19" style="26" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="15" style="26" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -37563,7 +37563,8 @@
   <dimension ref="A1:L998"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="27.5703125" customWidth="1"/>
+    <col min="1" max="4" width="27.5703125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="26"/>
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="7" max="7" width="36.140625" customWidth="1"/>
   </cols>
@@ -37662,10 +37663,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="1" max="1" width="28" style="26" customWidth="1"/>
+    <col min="2" max="2" width="19" style="26" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="15" style="26" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>

--- a/vSPD_Overrides/vSPD_Overrides.xlsx
+++ b/vSPD_Overrides/vSPD_Overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\vSPD\vSPD_Overrides\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB51E2E-0E52-4948-A7E0-279DBAB2E8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01801949-CB3F-4E72-8941-3433880F2D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -7590,6 +7590,7 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7599,7 +7600,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -36772,10 +36772,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="26" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="15" style="26" customWidth="1"/>
+    <col min="1" max="1" width="28" style="23" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15" style="23" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -36828,10 +36828,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="26" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="15" style="26" customWidth="1"/>
+    <col min="1" max="1" width="28" style="23" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15" style="23" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -36884,10 +36884,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="26" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="15" style="26" customWidth="1"/>
+    <col min="1" max="1" width="28" style="23" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15" style="23" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -36940,11 +36940,11 @@
   <dimension ref="A1:H96668"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="26" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
-    <col min="4" max="5" width="21.28515625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="15" style="26" customWidth="1"/>
+    <col min="1" max="1" width="28" style="23" customWidth="1"/>
+    <col min="2" max="2" width="56.140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="23" customWidth="1"/>
+    <col min="4" max="5" width="21.28515625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="15" style="23" customWidth="1"/>
     <col min="7" max="7" width="2.5703125" customWidth="1"/>
     <col min="8" max="8" width="36.140625" customWidth="1"/>
   </cols>
@@ -37032,12 +37032,12 @@
     </row>
     <row r="3" spans="2:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B3" s="9"/>
-      <c r="C3" s="23" t="str">
+      <c r="C3" s="24" t="str">
         <f>HYPERLINK("excel2gdx.bat","Click to create vSPD_Overrides.gdx")</f>
         <v>Click to create vSPD_Overrides.gdx</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
       <c r="F3" s="10"/>
     </row>
     <row r="4" spans="2:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -37189,11 +37189,11 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="19" style="26" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="19" style="26" customWidth="1"/>
-    <col min="5" max="5" width="15" style="26" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="19" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="19" style="23" customWidth="1"/>
+    <col min="5" max="5" width="15" style="23" customWidth="1"/>
     <col min="6" max="6" width="3.28515625" customWidth="1"/>
     <col min="7" max="7" width="36.140625" customWidth="1"/>
     <col min="8" max="35" width="9.140625" customWidth="1"/>
@@ -37221,19 +37221,19 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="23" t="s">
         <v>2113</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="23">
         <v>1.02</v>
       </c>
     </row>
@@ -37265,10 +37265,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="19" style="26" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="15" style="26" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="19" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15" style="23" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>
@@ -37321,8 +37321,8 @@
   <dimension ref="A1:L998"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="27.5703125" style="26" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="26"/>
+    <col min="1" max="4" width="27.5703125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="23"/>
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="7" max="7" width="36.140625" customWidth="1"/>
   </cols>
@@ -37421,9 +37421,9 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="27.5703125" style="26" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" style="26" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="26"/>
+    <col min="1" max="5" width="27.5703125" style="23" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="23" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="23"/>
     <col min="8" max="8" width="3" customWidth="1"/>
     <col min="9" max="9" width="36.140625" customWidth="1"/>
   </cols>
@@ -37563,8 +37563,8 @@
   <dimension ref="A1:L998"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="27.5703125" style="26" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="26"/>
+    <col min="1" max="4" width="27.5703125" style="23" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="23"/>
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="7" max="7" width="36.140625" customWidth="1"/>
   </cols>
@@ -37663,10 +37663,10 @@
   <dimension ref="A1:F96686"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" style="26" customWidth="1"/>
-    <col min="2" max="2" width="19" style="26" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="15" style="26" customWidth="1"/>
+    <col min="1" max="1" width="28" style="23" customWidth="1"/>
+    <col min="2" max="2" width="19" style="23" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="15" style="23" customWidth="1"/>
     <col min="5" max="5" width="2.5703125" customWidth="1"/>
     <col min="6" max="6" width="36.140625" customWidth="1"/>
   </cols>

--- a/vSPD_Overrides/vSPD_Overrides.xlsx
+++ b/vSPD_Overrides/vSPD_Overrides.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\vSPD\vSPD_Overrides\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8344B581-E20C-4CCC-9FAD-F3F0BF8A5305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FC60CA-DCDF-4948-85B0-5CCA9A02653F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -914,7 +914,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="2111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2182" uniqueCount="2111">
   <si>
     <t>Value</t>
   </si>
@@ -36792,6 +36792,20 @@
         <v>Go back to Main worksheet</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D2" s="23">
+        <v>554</v>
+      </c>
+    </row>
     <row r="96686" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E96686" s="19" t="s">
         <v>190</v>
@@ -36847,6 +36861,48 @@
       <c r="F1" s="17" t="str">
         <f>HYPERLINK("[vSPD_Overrides.xlsx]Main!A1","Go back to Main worksheet")</f>
         <v>Go back to Main worksheet</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D2" s="23">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="23">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>649</v>
+      </c>
+      <c r="D4" s="23">
+        <v>-2</v>
       </c>
     </row>
     <row r="96686" spans="5:5" x14ac:dyDescent="0.25">
